--- a/日報/日報_テスト三郎.xlsx
+++ b/日報/日報_テスト三郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\日報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F4389F-3E20-4050-A89C-76E3D31869C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1418B960-445A-402A-BC90-622723B3DF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/日報/日報_テスト三郎.xlsx
+++ b/日報/日報_テスト三郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\日報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1418B960-445A-402A-BC90-622723B3DF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F941C714-4628-43A5-9A34-47B2AFFB3D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7410" yWindow="7410" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
